--- a/data/trans_camb/IP19C07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 12,38</t>
+          <t>-23,13; 13,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 13,65</t>
+          <t>-19,18; 14,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 8,2</t>
+          <t>-22,11; 7,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 16,88</t>
+          <t>-11,94; 17,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 14,79</t>
+          <t>-13,79; 12,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 4,78</t>
+          <t>-20,54; 4,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 9,85</t>
+          <t>-12,13; 11,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 10,3</t>
+          <t>-11,35; 9,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 2,84</t>
+          <t>-16,0; 3,48</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 184,09</t>
+          <t>-88,61; 287,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,01; 204,9</t>
+          <t>-77,32; 262,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,84; 145,41</t>
+          <t>-81,96; 111,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,48; 428,93</t>
+          <t>-77,8; 550,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,93; 478,26</t>
+          <t>-82,32; 405,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 124,72</t>
+          <t>-64,38; 166,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,82; 133,82</t>
+          <t>-61,17; 146,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 46,36</t>
+          <t>-76,71; 70,15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 8,19</t>
+          <t>-5,57; 7,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 13,3</t>
+          <t>-3,53; 13,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 17,13</t>
+          <t>-0,54; 15,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 10,93</t>
+          <t>-3,42; 10,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 0,78</t>
+          <t>-9,02; 1,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 15,31</t>
+          <t>-2,37; 14,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 7,74</t>
+          <t>-2,5; 6,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 5,94</t>
+          <t>-3,93; 5,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,96</t>
+          <t>1,1; 12,92</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 478,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-68,91; 846,73</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-24,49; 869,13</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-60,69; 693,45</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-29,81; 898,18</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-54,18; 730,45</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 845,36</t>
+          <t>-52,96; 950,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 314,88</t>
+          <t>-41,9; 276,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 246,94</t>
+          <t>-68,42; 259,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 529,86</t>
+          <t>9,32; 510,91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 10,01</t>
+          <t>-22,04; 10,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -9,58</t>
+          <t>-35,74; -10,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,3; -3,18</t>
+          <t>-33,01; -4,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 9,08</t>
+          <t>-18,31; 9,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -10,68</t>
+          <t>-30,63; -10,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,51; -8,01</t>
+          <t>-30,64; -8,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 6,84</t>
+          <t>-15,92; 5,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,43; -12,57</t>
+          <t>-29,37; -12,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,39; -10,86</t>
+          <t>-27,53; -10,25</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 64,67</t>
+          <t>-68,0; 67,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,16</t>
+          <t>-100,0; -25,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,85</t>
+          <t>-94,09; -11,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,23; 79,35</t>
+          <t>-69,17; 84,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -46,19</t>
+          <t>-100,0; -35,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 45,13</t>
+          <t>-58,91; 39,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -61,23</t>
+          <t>-100,0; -62,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-95,78; -59,26</t>
+          <t>-95,36; -55,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 3,07</t>
+          <t>-20,83; 2,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,01; -8,7</t>
+          <t>-26,26; -8,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 6,94</t>
+          <t>-18,76; 6,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -2,51</t>
+          <t>-26,1; -2,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,64; -10,49</t>
+          <t>-31,32; -10,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,02; -9,95</t>
+          <t>-29,94; -9,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,32; -2,89</t>
+          <t>-19,18; -3,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,98; -11,61</t>
+          <t>-24,74; -10,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -5,65</t>
+          <t>-21,39; -5,7</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,0; 57,21</t>
+          <t>-87,57; 38,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,83; 97,16</t>
+          <t>-86,72; 78,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-94,66; 15,9</t>
+          <t>-94,94; 7,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -66,29</t>
+          <t>-100,0; -69,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,1; -13,39</t>
+          <t>-84,98; -16,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-91,86; -25,68</t>
+          <t>-93,54; -33,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 5,39</t>
+          <t>-12,7; 5,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 26,84</t>
+          <t>-3,53; 27,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 9,87</t>
+          <t>-10,63; 9,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 19,41</t>
+          <t>-2,3; 19,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,92; 42,47</t>
+          <t>5,93; 43,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 5,95</t>
+          <t>-8,8; 6,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 10,13</t>
+          <t>-4,49; 10,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,52; 28,87</t>
+          <t>4,8; 30,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 5,36</t>
+          <t>-7,66; 5,57</t>
         </is>
       </c>
     </row>
@@ -1677,24 +1677,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>-81,22; —</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-9,05; —</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 1994,39</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 17,18</t>
+          <t>-13,76; 16,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 11,56</t>
+          <t>-17,47; 10,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,97; -2,72</t>
+          <t>-25,15; -1,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 9,54</t>
+          <t>-18,93; 8,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -2,25</t>
+          <t>-27,13; -1,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -6,88</t>
+          <t>-27,64; -6,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 9,58</t>
+          <t>-11,25; 9,22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 1,03</t>
+          <t>-16,36; 1,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-21,94; -6,92</t>
+          <t>-23,47; -7,15</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 275,25</t>
+          <t>-63,63; 358,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 196,44</t>
+          <t>-77,13; 239,53</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 125,87</t>
+          <t>-80,34; 107,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,72</t>
+          <t>-100,0; 28,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 110,58</t>
+          <t>-55,21; 101,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-80,78; 16,01</t>
+          <t>-79,55; 30,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -59,96</t>
+          <t>-100,0; -59,94</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 12,68</t>
+          <t>-7,66; 11,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 6,76</t>
+          <t>-11,86; 6,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 4,98</t>
+          <t>-12,89; 5,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 15,51</t>
+          <t>-3,33; 13,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 2,73</t>
+          <t>-11,56; 2,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 6,02</t>
+          <t>-8,31; 6,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 10,23</t>
+          <t>-2,85; 10,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 3,18</t>
+          <t>-8,94; 2,67</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,46</t>
+          <t>-8,22; 3,15</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 166,56</t>
+          <t>-45,02; 117,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 87,5</t>
+          <t>-65,43; 71,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 64,21</t>
+          <t>-70,72; 70,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 352,17</t>
+          <t>-35,45; 312,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-91,25; 108,51</t>
+          <t>-92,74; 118,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 150,12</t>
+          <t>-65,67; 168,11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 130,77</t>
+          <t>-24,03; 133,7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-67,85; 41,88</t>
+          <t>-66,01; 34,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,27; 48,52</t>
+          <t>-58,74; 43,3</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 0,03</t>
+          <t>-13,51; -0,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 4,28</t>
+          <t>-10,37; 4,51</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 0,3</t>
+          <t>-13,71; 0,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 4,46</t>
+          <t>-7,35; 4,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 11,76</t>
+          <t>-3,07; 12,32</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 8,25</t>
+          <t>-5,03; 8,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 0,8</t>
+          <t>-8,9; 0,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 6,18</t>
+          <t>-4,63; 5,89</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 2,32</t>
+          <t>-7,28; 2,66</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-87,66; 17,38</t>
+          <t>-89,77; 17,98</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 67,41</t>
+          <t>-70,72; 81,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,92; 26,23</t>
+          <t>-90,17; 49,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-79,24; 163,32</t>
+          <t>-83,91; 161,06</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 350,62</t>
+          <t>-41,38; 372,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 248,97</t>
+          <t>-57,98; 254,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-76,92; 20,9</t>
+          <t>-77,18; 19,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 109,48</t>
+          <t>-40,79; 102,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 41,86</t>
+          <t>-62,65; 49,72</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,16</t>
+          <t>-6,6; 1,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,41</t>
+          <t>-8,03; -0,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,72</t>
+          <t>-8,19; -0,93</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,41</t>
+          <t>-3,89; 3,43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,37</t>
+          <t>-7,2; -0,97</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -1,11</t>
+          <t>-7,31; -1,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,39</t>
+          <t>-3,95; 1,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,63</t>
+          <t>-6,88; -1,98</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -2,2</t>
+          <t>-6,95; -2,04</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 11,65</t>
+          <t>-45,46; 14,07</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-56,74; -4,1</t>
+          <t>-54,28; -4,24</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-57,5; -5,63</t>
+          <t>-55,66; -8,06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 41,55</t>
+          <t>-32,63; 39,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-64,08; -14,62</t>
+          <t>-62,73; -11,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-62,67; -12,31</t>
+          <t>-62,02; -11,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 13,27</t>
+          <t>-31,7; 11,17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -16,19</t>
+          <t>-53,69; -18,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -22,85</t>
+          <t>-56,04; -20,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 13,39</t>
+          <t>-21,37; 12,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 14,47</t>
+          <t>-19,28; 16,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 7,31</t>
+          <t>-22,58; 8,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 17,88</t>
+          <t>-13,66; 16,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 12,94</t>
+          <t>-14,46; 12,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 4,53</t>
+          <t>-21,06; 3,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 11,05</t>
+          <t>-12,42; 10,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 9,54</t>
+          <t>-11,96; 10,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 3,48</t>
+          <t>-16,69; 2,42</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-88,61; 287,23</t>
+          <t>-86,39; 246,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 262,82</t>
+          <t>-74,28; 275,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,96; 111,05</t>
+          <t>-83,64; 180,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 550,8</t>
+          <t>-75,37; 433,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 405,08</t>
+          <t>-85,42; 340,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 149,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 166,62</t>
+          <t>-65,51; 133,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 146,65</t>
+          <t>-60,26; 157,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,71; 70,15</t>
+          <t>-81,13; 35,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 7,58</t>
+          <t>-5,26; 7,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 13,35</t>
+          <t>-3,21; 13,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 15,93</t>
+          <t>-1,13; 15,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 10,41</t>
+          <t>-3,48; 10,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,23</t>
+          <t>-8,74; 0,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 14,09</t>
+          <t>-2,31; 14,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,82</t>
+          <t>-2,32; 7,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 5,91</t>
+          <t>-3,9; 5,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 12,92</t>
+          <t>0,73; 13,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-77,29; 1416,99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-66,09; 833,64</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-27,6; 915,76</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-62,03; 684,95</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-68,91; 846,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-24,49; 869,13</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-60,69; 693,45</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 950,51</t>
+          <t>-50,95; 855,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 276,51</t>
+          <t>-42,53; 324,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 259,92</t>
+          <t>-67,63; 253,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 510,91</t>
+          <t>-0,97; 512,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 10,42</t>
+          <t>-22,32; 12,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,74; -10,47</t>
+          <t>-35,85; -9,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -4,77</t>
+          <t>-31,7; -4,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 9,28</t>
+          <t>-18,53; 9,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -10,68</t>
+          <t>-32,0; -10,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -8,9</t>
+          <t>-30,72; -9,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 5,43</t>
+          <t>-15,91; 5,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,37; -12,66</t>
+          <t>-29,85; -13,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,53; -10,25</t>
+          <t>-28,02; -10,6</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 67,09</t>
+          <t>-67,84; 72,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,67</t>
+          <t>-100,0; -34,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-94,09; -11,92</t>
+          <t>-93,55; -6,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 84,44</t>
+          <t>-67,73; 91,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -35,24</t>
+          <t>-100,0; -58,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 39,26</t>
+          <t>-58,58; 38,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -62,71</t>
+          <t>-100,0; -64,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-95,36; -55,46</t>
+          <t>-95,58; -54,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 2,0</t>
+          <t>-20,73; 3,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,26; -8,55</t>
+          <t>-28,16; -8,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 6,02</t>
+          <t>-18,61; 6,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,1; -2,66</t>
+          <t>-26,47; -1,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,32; -10,43</t>
+          <t>-30,62; -10,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -9,85</t>
+          <t>-30,35; -9,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,18; -3,85</t>
+          <t>-19,57; -3,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -10,97</t>
+          <t>-25,78; -11,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,39; -5,7</t>
+          <t>-21,75; -6,03</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 38,71</t>
+          <t>-86,17; 47,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 78,68</t>
+          <t>-87,75; 98,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-94,94; 7,31</t>
+          <t>-93,88; 1,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -69,28</t>
+          <t>-100,0; -51,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,98; -16,58</t>
+          <t>-83,49; -15,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-93,54; -33,08</t>
+          <t>-93,35; -28,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 5,37</t>
+          <t>-12,49; 5,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 27,72</t>
+          <t>-5,62; 26,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 9,58</t>
+          <t>-10,46; 8,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 19,69</t>
+          <t>-3,44; 20,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,93; 43,66</t>
+          <t>6,59; 45,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,44</t>
+          <t>-9,21; 6,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 10,37</t>
+          <t>-4,77; 9,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 30,53</t>
+          <t>3,3; 31,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 5,57</t>
+          <t>-6,78; 5,04</t>
         </is>
       </c>
     </row>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-81,22; —</t>
+          <t>-77,3; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,05; —</t>
+          <t>8,29; 1883,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 16,62</t>
+          <t>-13,19; 17,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 10,93</t>
+          <t>-15,29; 11,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -1,14</t>
+          <t>-27,11; -3,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 8,6</t>
+          <t>-18,34; 9,74</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-27,13; -1,23</t>
+          <t>-25,21; -2,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -6,7</t>
+          <t>-27,52; -6,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 9,22</t>
+          <t>-11,24; 9,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 1,81</t>
+          <t>-16,65; 1,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,47; -7,15</t>
+          <t>-23,03; -7,38</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 358,05</t>
+          <t>-63,9; 342,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 239,53</t>
+          <t>-74,41; 268,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-80,34; 107,1</t>
+          <t>-80,23; 143,21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,95</t>
+          <t>-100,0; 28,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-55,21; 101,82</t>
+          <t>-57,23; 97,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-79,55; 30,08</t>
+          <t>-80,01; 28,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -59,94</t>
+          <t>-100,0; -57,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 11,04</t>
+          <t>-8,19; 10,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 6,72</t>
+          <t>-12,14; 6,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 5,54</t>
+          <t>-12,87; 5,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 13,41</t>
+          <t>-3,95; 14,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 2,51</t>
+          <t>-12,45; 1,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,64</t>
+          <t>-8,31; 6,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 10,08</t>
+          <t>-3,28; 10,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 2,67</t>
+          <t>-9,18; 2,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 3,15</t>
+          <t>-8,09; 2,84</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 117,09</t>
+          <t>-45,09; 124,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 71,84</t>
+          <t>-66,83; 86,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 70,84</t>
+          <t>-68,53; 85,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 312,27</t>
+          <t>-34,58; 298,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-92,74; 118,43</t>
+          <t>-100,0; 95,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 168,11</t>
+          <t>-63,54; 168,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 133,7</t>
+          <t>-24,43; 128,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 34,31</t>
+          <t>-66,0; 37,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 43,3</t>
+          <t>-57,06; 38,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -0,25</t>
+          <t>-13,42; -0,33</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 4,51</t>
+          <t>-10,99; 3,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 0,19</t>
+          <t>-14,23; -0,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,79</t>
+          <t>-7,47; 4,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 12,32</t>
+          <t>-1,92; 12,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 8,0</t>
+          <t>-4,68; 8,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 0,77</t>
+          <t>-8,59; 0,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,89</t>
+          <t>-4,58; 6,43</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 2,66</t>
+          <t>-7,45; 2,83</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-89,77; 17,98</t>
+          <t>-89,39; 5,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 81,01</t>
+          <t>-75,84; 66,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-90,17; 49,79</t>
+          <t>-92,97; 6,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-83,91; 161,06</t>
+          <t>-83,67; 189,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 372,78</t>
+          <t>-26,76; 393,93</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 254,0</t>
+          <t>-52,21; 301,76</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 19,33</t>
+          <t>-77,27; 11,91</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 102,2</t>
+          <t>-42,2; 116,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 49,72</t>
+          <t>-66,9; 62,72</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,34</t>
+          <t>-6,23; 1,17</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,55</t>
+          <t>-7,75; -0,2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,19; -0,93</t>
+          <t>-8,13; -0,42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,43</t>
+          <t>-3,38; 3,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -0,97</t>
+          <t>-7,59; -1,17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -1,21</t>
+          <t>-7,37; -1,02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,12</t>
+          <t>-3,88; 1,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -1,98</t>
+          <t>-6,7; -1,74</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -2,04</t>
+          <t>-6,93; -1,95</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 14,07</t>
+          <t>-45,41; 11,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -4,24</t>
+          <t>-54,44; -0,01</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-55,66; -8,06</t>
+          <t>-56,97; -3,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 39,54</t>
+          <t>-28,93; 43,2</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -11,96</t>
+          <t>-63,7; -14,02</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-62,02; -11,9</t>
+          <t>-62,85; -11,88</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 11,17</t>
+          <t>-31,61; 13,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -18,39</t>
+          <t>-53,27; -17,23</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -20,89</t>
+          <t>-55,45; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-4,37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,43</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,62</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-4,85</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 12,33</t>
+          <t>-13,79; 16,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 16,21</t>
+          <t>-14,53; 14,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 8,45</t>
+          <t>-18,3; 5,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 16,97</t>
+          <t>-22,52; 12,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 12,62</t>
+          <t>-20,91; 13,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 3,95</t>
+          <t>-20,89; 10,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 10,33</t>
+          <t>-11,44; 9,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 10,76</t>
+          <t>-12,2; 10,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 2,42</t>
+          <t>-15,9; 3,98</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-0,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-49,05%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-26,8%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-8,77%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-34,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,48%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-53,48%</t>
+          <t>-27,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-41,96%</t>
+          <t>-36,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-86,39; 246,36</t>
+          <t>-77,48; 428,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 275,64</t>
+          <t>-78,93; 478,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,64; 180,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-75,37; 433,88</t>
+          <t>-87,1; 184,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,42; 340,23</t>
+          <t>-83,01; 204,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,82</t>
+          <t>-79,72; 147,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 133,93</t>
+          <t>-61,69; 124,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,26; 157,7</t>
+          <t>-61,82; 133,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,13; 35,82</t>
+          <t>-74,86; 65,88</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,91</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,81</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>8,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 7,96</t>
+          <t>-2,85; 10,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 13,37</t>
+          <t>-8,72; 0,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 15,42</t>
+          <t>-2,19; 14,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 10,32</t>
+          <t>-5,55; 8,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,55</t>
+          <t>-3,97; 13,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 14,1</t>
+          <t>0,87; 18,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,04</t>
+          <t>-2,56; 7,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,43</t>
+          <t>-4,06; 5,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 13,13</t>
+          <t>1,49; 13,62</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-71,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>113,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>84,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>166,94%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80,8%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-71,56%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>119,72%</t>
+          <t>184,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>143,14%</t>
+          <t>149,5%</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,29; 1416,99</t>
+          <t>-54,18; 730,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 833,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 915,76</t>
+          <t>-50,13; 857,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 684,95</t>
+          <t>-85,33; 478,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 855,45</t>
+          <t>-24,56; 957,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,53; 324,48</t>
+          <t>-45,1; 314,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,63; 253,46</t>
+          <t>-72,63; 246,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 512,8</t>
+          <t>12,47; 530,86</t>
         </is>
       </c>
     </row>
@@ -1056,29 +1056,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-19,64</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-18,35</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-5,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-21,89</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-18,21</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,4</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-19,64</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-18,26</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-18,48</t>
+          <t>-18,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 12,1</t>
+          <t>-18,27; 9,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -9,33</t>
+          <t>-30,48; -10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-31,7; -4,44</t>
+          <t>-30,65; -8,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 9,59</t>
+          <t>-23,36; 10,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,0; -10,7</t>
+          <t>-35,43; -9,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,72; -9,35</t>
+          <t>-33,28; -3,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 5,62</t>
+          <t>-14,42; 6,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,85; -13,46</t>
+          <t>-29,43; -12,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -10,6</t>
+          <t>-27,18; -10,67</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-22,41%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-93,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-22,15%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-89,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-74,45%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-93,02%</t>
+          <t>-74,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-83,96%</t>
+          <t>-83,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 72,95</t>
+          <t>-66,23; 79,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -34,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,55; -6,61</t>
+          <t>-100,0; -47,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 91,15</t>
+          <t>-71,19; 64,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -31,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -58,45</t>
+          <t>-100,0; -4,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 38,92</t>
+          <t>-54,66; 45,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,48</t>
+          <t>-100,0; -61,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-95,58; -54,13</t>
+          <t>-95,58; -57,2</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-13,48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-19,11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-18,27</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-8,29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-15,97</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-13,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-19,11</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-18,2</t>
+          <t>-6,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,13</t>
+          <t>-12,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 3,14</t>
+          <t>-25,78; -2,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-28,16; -8,8</t>
+          <t>-29,64; -10,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 6,62</t>
+          <t>-29,92; -9,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,47; -1,86</t>
+          <t>-20,01; 3,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,62; -10,44</t>
+          <t>-26,01; -8,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,35; -9,67</t>
+          <t>-18,23; 8,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -3,31</t>
+          <t>-19,32; -2,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -11,77</t>
+          <t>-25,98; -11,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,75; -6,03</t>
+          <t>-20,21; -4,53</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-70,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-95,62%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-51,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-42,4%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-70,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-37,91%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-62,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-95,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-62,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-74,88%</t>
+          <t>-71,64%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,17; 47,83</t>
+          <t>-94,66; 15,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 98,97</t>
+          <t>-100,0; -69,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-93,88; 1,5</t>
+          <t>-89,0; 57,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,91</t>
+          <t>-85,39; 113,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-83,49; -15,67</t>
+          <t>-85,1; -13,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-93,35; -28,47</t>
+          <t>-90,9; -16,24</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>22,42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,58</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>8,15</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>22,42</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>0,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 5,3</t>
+          <t>-2,92; 19,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 26,0</t>
+          <t>5,92; 42,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 8,51</t>
+          <t>-8,6; 6,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 20,18</t>
+          <t>-13,19; 5,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,59; 45,94</t>
+          <t>-5,7; 26,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 6,29</t>
+          <t>-10,54; 10,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 9,28</t>
+          <t>-3,98; 10,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 31,36</t>
+          <t>4,52; 28,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,04</t>
+          <t>-6,81; 5,73</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>248,64%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>757,09%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-49,35%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>156,16%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-2,76%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>248,64%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>757,09%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>-1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-3,81%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-77,3; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,29; 1883,57</t>
+          <t>1,98; 1994,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-3,75</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-12,07</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-15,72</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,83</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-11,62</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-3,75</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-12,07</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-15,72</t>
+          <t>-11,48</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-13,74</t>
+          <t>-13,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 17,2</t>
+          <t>-18,56; 9,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 11,67</t>
+          <t>-27,64; -2,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-27,11; -3,1</t>
+          <t>-31,24; -6,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 9,74</t>
+          <t>-12,26; 17,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -2,61</t>
+          <t>-16,51; 11,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -6,65</t>
+          <t>-25,77; -2,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 9,28</t>
+          <t>-10,75; 9,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 1,32</t>
+          <t>-16,88; 1,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,03; -7,38</t>
+          <t>-21,86; -6,66</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-23,85%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-76,82%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>18,79%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-13,73%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-87,4%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-23,85%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-76,82%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-86,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-94,25%</t>
+          <t>-93,36%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 342,42</t>
+          <t>-78,5; 125,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 268,23</t>
+          <t>-100,0; 27,72</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 143,21</t>
+          <t>-60,95; 275,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,22</t>
+          <t>-80,51; 196,44</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 97,81</t>
+          <t>-51,92; 110,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-80,01; 28,98</t>
+          <t>-80,78; 16,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -57,62</t>
+          <t>-100,0; -54,31</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,16</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,53</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,58</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,09</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,53</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-1,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 10,41</t>
+          <t>-3,22; 15,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 6,92</t>
+          <t>-11,04; 2,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 5,98</t>
+          <t>-7,33; 7,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 14,21</t>
+          <t>-8,31; 12,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 1,9</t>
+          <t>-12,22; 6,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,71</t>
+          <t>-13,1; 5,85</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 10,14</t>
+          <t>-3,19; 10,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 2,95</t>
+          <t>-9,55; 3,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 2,84</t>
+          <t>-7,72; 4,47</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-53,37%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>12,23%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-19,0%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-30,11%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>60,86%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-53,37%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-8,29%</t>
+          <t>-26,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-22,65%</t>
+          <t>-16,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 124,15</t>
+          <t>-32,75; 352,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,83; 86,81</t>
+          <t>-91,25; 108,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 85,33</t>
+          <t>-63,03; 174,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 298,45</t>
+          <t>-47,21; 166,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,27</t>
+          <t>-65,45; 87,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-63,54; 168,76</t>
+          <t>-70,83; 77,94</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 128,5</t>
+          <t>-25,0; 130,77</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 37,57</t>
+          <t>-67,85; 41,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 38,42</t>
+          <t>-53,32; 57,84</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,39</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4,68</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-6,18</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-2,79</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-6,47</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>-6,73</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,35</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -0,33</t>
+          <t>-7,29; 4,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 3,98</t>
+          <t>-2,27; 11,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -0,65</t>
+          <t>-4,63; 8,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,62</t>
+          <t>-13,42; 0,03</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 12,14</t>
+          <t>-10,49; 4,28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,2</t>
+          <t>-13,35; -0,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 0,36</t>
+          <t>-8,63; 0,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 6,43</t>
+          <t>-4,57; 6,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,83</t>
+          <t>-7,26; 2,19</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-22,51%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>29,81%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-59,34%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-26,75%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-62,13%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-22,51%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>75,49%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>-64,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-26,86%</t>
+          <t>-28,01%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 5,47</t>
+          <t>-79,24; 163,32</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-75,84; 66,3</t>
+          <t>-33,41; 350,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-92,97; 6,54</t>
+          <t>-53,06; 252,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-83,67; 189,66</t>
+          <t>-87,66; 17,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 393,93</t>
+          <t>-72,72; 67,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 301,76</t>
+          <t>-90,85; 19,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-77,27; 11,91</t>
+          <t>-76,92; 20,9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 116,79</t>
+          <t>-42,38; 109,48</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 62,72</t>
+          <t>-66,28; 41,66</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-4,34</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-3,96</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-2,54</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-4,47</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-4,34</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-4,26</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,17</t>
+          <t>-3,88; 3,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -0,2</t>
+          <t>-7,89; -1,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -0,42</t>
+          <t>-7,66; -0,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,51</t>
+          <t>-6,7; 1,16</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,17</t>
+          <t>-7,99; -0,41</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -1,02</t>
+          <t>-8,17; -0,55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,36</t>
+          <t>-3,82; 1,39</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,74</t>
+          <t>-6,61; -1,63</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,95</t>
+          <t>-6,78; -1,81</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-1,37%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-43,3%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-39,55%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-20,81%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-33,16%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-1,37%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-43,3%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-42,53%</t>
+          <t>-35,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-40,13%</t>
+          <t>-37,62%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 11,58</t>
+          <t>-32,19; 41,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -0,01</t>
+          <t>-64,08; -14,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,97; -3,72</t>
+          <t>-61,28; -8,3</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 43,2</t>
+          <t>-46,71; 11,65</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-63,7; -14,02</t>
+          <t>-56,74; -4,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -11,88</t>
+          <t>-56,65; -2,17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 13,8</t>
+          <t>-30,64; 13,27</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -17,23</t>
+          <t>-52,34; -16,19</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-55,45; -18,78</t>
+          <t>-54,68; -19,02</t>
         </is>
       </c>
     </row>
